--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0019.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0019.xlsx
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Cậu... Tại sao cậu lại...</t>
+          <t>Mày... Tại sao mày lại...</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Ta không thể để ngươi chiến đấu một mình được.</t>
+          <t>Tao không thể để mày chiến đấu một mình được.</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Anh chắc không?</t>
+          <t>Cậu chắc chắn chứ?</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Ta muốn sống. Ta muốn trở thành một người trưởng thành mạnh mẽ.</t>
+          <t>Tao muốn sống. Tao muốn trở thành một người trưởng thành mạnh mẽ.</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Ta muốn trở nên mạnh mẽ như cậu...</t>
+          <t>Tao muốn trở nên mạnh mẽ như cậu...</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>(Đây là những ký ức của ta... tái hiện bên trong Quả Cầu Sonoro này.)</t>
+          <t>(Đây là những ký ức của ta... tái hiện bên trong Sonoro Sphere này.)</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Cái này... ừm, nếu ta đốt nó một chút bằng lửa... thì có lẽ ăn được?</t>
+          <t>Cái này... ừm, nếu tao đốt nó một chút bằng lửa... thì có lẽ ăn được?</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Đừng có giở trò với ta, tên trộm nhãi.</t>
+          <t>Đừng có giở trò với tao, tên trộm nhãi.</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Ha! Làm gì có chuyện hoang đường thế? Một đứa nhóc vô gia cư như cậu mà kiếm được đống thức ăn này sao?</t>
+          <t>Ha! Làm gì có chuyện hoang đường thế? Một đứa nhóc vô gia cư như mày mà kiếm được đống thức ăn này sao?</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>??y l? l?nh ??a c?a ch?ng ta. Bi?t ?i?u th? r?i ?i ngay...</t>
+          <t>Đây là lãnh địa của chúng tao. Biết điều thì cút ngay đi...</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Ừ, hồi đó ta không biết cách kiểm soát ngọn lửa của mình. Chỉ biết dùng sức mạnh thô để thoát ra, cả người lúc nào cũng đầy vết bỏng...</t>
+          <t>Ừ, hồi đó tao không biết cách kiểm soát ngọn lửa của mình. Chỉ biết dùng sức mạnh thô để thoát ra, cả người lúc nào cũng đầy vết bỏng...</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Tôi là Cộng Hưởng Giả. Những vết thương này chẳng là gì cả.</t>
+          <t>Tôi là Resonator. Những vết thương này chẳng là gì cả.</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>(Không gian bên trong Quả Cầu Sonoro này thật hỗn độn...)</t>
+          <t>(Không gian bên trong Sonoro Sphere này thật hỗn độn...)</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Ta muốn sống, học cách kiểm soát sức mạnh của mình và trở nên mạnh mẽ hơn... Nếu không, ta sẽ chẳng bao giờ thấy được một thế giới bình yên và thịnh vượng...</t>
+          <t>Tao muốn sống, học cách kiểm soát sức mạnh của mình và trở nên mạnh mẽ hơn... Nếu không, tao sẽ chẳng bao giờ thấy được một thế giới bình yên và thịnh vượng...</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>{Male=Anh ấy;Female=Cô ấy} là người duy nhất có thể thay đổi thế giới này. Ngươi phải tìm {Male=anh ấy;Female=cô ấy} và giúp đỡ {Male=anh ấy;Female=cô ấy}.</t>
+          <t>{Male=him;Female=her} là người duy nhất có thể thay đổi thế giới này. Ngươi phải tìm {Male=him;Female=her} và giúp đỡ {Male=him;Female=her}.</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>(...Bàn cờ Vây này, và Quả Cầu Sonoro... Cả hai đều là một câu đố và cũng là lời giải.)</t>
+          <t>(...Bàn cờ Vây này, và Sonoro Sphere... Cả hai đều là một câu đố và cũng là lời giải.)</t>
         </is>
       </c>
     </row>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>(Kết thúc của Sonoro Sphere này... hóa ra lại chính là nơi {Male=hắn;Female=cô ta} đang ở.)</t>
+          <t>(Kết thúc của Sonoro Sphere này... hóa ra lại chính là nơi {Male=he;Female=she} đang ở.)</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Cậu ổn chứ?</t>
+          <t>Cậu ổn không?</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Cậu tìm cái gì?</t>
+          <t>Mày tìm cái gì?</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Ta không biết... Nhưng ta nhớ nó cực kỳ quan trọng, thứ gì đó có thể thay đổi cả thế giới...</t>
+          <t>Tao không biết... Nhưng tao nhớ nó cực kỳ quan trọng, thứ gì đó có thể thay đổi cả thế giới...</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Nhưng giờ ta bắt đầu tự hỏi mình đến đây làm gì nữa... Mọi thứ khác xa những gì ta nhớ...</t>
+          <t>Nhưng giờ tao bắt đầu tự hỏi mình đến đây làm gì nữa... Mọi thứ khác xa những gì tao nhớ...</t>
         </is>
       </c>
     </row>
@@ -9739,7 +9739,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Run!!</t>
+          <t>Chạy mau!!</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Okay..</t>
+          <t>Ừm...</t>
         </is>
       </c>
     </row>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Ở đây! Ta đợi ngươi lâu rồi đấy!</t>
+          <t>Ở đây! Tao đợi mày lâu rồi đấy!</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Ta tưởng Yangyang bảo ngươi có một đứa bạn siêu ngầu nhỏ xíu để giới thiệu cho tụi ta. Nó đâu rồi?</t>
+          <t>Tao tưởng Yangyang bảo mày có một đứa bạn siêu ngầu nhỏ xíu để giới thiệu cho tụi tao. Nó đâu rồi?</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Cậu chắc không pha thêm gì vào chứ?</t>
+          <t>Mày chắc không pha thêm gì vào chứ?</t>
         </is>
       </c>
     </row>
@@ -12794,7 +12794,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Nghe không giống Baizhi mà ta biết...</t>
+          <t>Nghe không giống Baizhi mà tao biết...</t>
         </is>
       </c>
     </row>
@@ -13444,7 +13444,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Cậu có biết chính xác {Male=hắn;Female=cô ta} đã hấp thụ cậu ở đâu không?</t>
+          <t>Cậu có biết chính xác {Male=he;Female=she} đã hấp thụ cậu ở đâu không?</t>
         </is>
       </c>
     </row>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Hả? Làm sao ta biết được... Sao cậu không hỏi thẳng {Male=hắn;Female=cô ta} đi?</t>
+          <t>Hả? Làm sao tao biết được... Sao cậu không hỏi thẳng {Male=him;Female=her} đi?</t>
         </is>
       </c>
     </row>
@@ -13704,7 +13704,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Ừ. Chuyện đó xảy ra trước khi {Male=cậu ấy;Female=cô ấy} mất hết ký ức, nên chỉ có cậu mới biết.</t>
+          <t>Ừ. Chuyện đó xảy ra trước khi {Male=he;Female=she} mất hết ký ức, nên chỉ có cậu mới biết.</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Tsk tsk... Đừng có mà nói giọng đó với ta.</t>
+          <t>Tsk tsk... Đừng có mà nói giọng đó với tao.</t>
         </is>
       </c>
     </row>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Thằng tóc xanh kia cũng hỏi ta câu tương tự. Xin lỗi nhé, nhưng ta thực sự chẳng nhớ gì trước khi xuất hiện ở đây cả.</t>
+          <t>Thằng tóc xanh kia cũng hỏi tao câu tương tự. Xin lỗi nhé, nhưng tao thực sự chẳng nhớ gì trước khi xuất hiện ở đây cả.</t>
         </is>
       </c>
     </row>
@@ -13964,7 +13964,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Hừm. Có khi... có khi mình chỉ ngủ quên trong người {Male=anh ấy;Female=cô ấy} suốt thời gian qua, nên mới chẳng nhớ gì cả!</t>
+          <t>Hừm. Có khi... có khi mình chỉ ngủ quên trong người {Male=him;Female=her} suốt thời gian qua, nên mới chẳng nhớ gì cả!</t>
         </is>
       </c>
     </row>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Hừm, ta cứ tưởng ngươi sẽ khác hẳn mấy đứa thường thấy cơ. Ai dè lại giống y chang.</t>
+          <t>Hừm, tao cứ tưởng mày sẽ khác hẳn mấy đứa thường thấy cơ. Ai dè lại giống y chang.</t>
         </is>
       </c>
     </row>
@@ -15069,7 +15069,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Hừ! Đừng có coi thường ta!</t>
+          <t>Hừ! Đừng có coi thường tao!</t>
         </is>
       </c>
     </row>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Đúng rồi, ta muốn nó ngay bây giờ! Nhìn này, tên ngươi là Chixia, tên ngươi là Yangyang, còn ngươi... Ơ, tên ngươi là...</t>
+          <t>Đúng rồi, tao muốn nó ngay bây giờ! Nhìn này, tên mày là Chixia, tên mày là Yangyang, còn mày... Ơ, tên mày là...</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Ừ, đúng như cô ấy nói đấy! Mỗi người trong các cậu đều có tên, và ta cũng muốn có một cái cho riêng mình! Đâu có đòi hỏi gì nhiều đâu.</t>
+          <t>Ừ, đúng như cô ấy nói đấy! Mỗi người trong các cậu đều có tên, và tao cũng muốn có một cái cho riêng mình! Đâu có đòi hỏi gì nhiều đâu.</t>
         </is>
       </c>
     </row>
@@ -16109,7 +16109,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Không, không đời nào! Cái đó thẳng thừng quá. Chẳng khác nào gọi ta là "thằng nhóc"!</t>
+          <t>Không, không đời nào! Cái đó thẳng thừng quá. Chẳng khác nào gọi tao là "thằng nhóc"!</t>
         </is>
       </c>
     </row>
@@ -17669,7 +17669,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Tất nhiên là ta thích rồi! Chính cậu đặt cho ta mà! Ta chỉ... cố làm quen thôi! Hơn nữa, giờ ta thấy gắn bó với cái tên này lắm rồi!</t>
+          <t>Tất nhiên là tao thích rồi! Chính cậu đặt cho tao mà! Tao chỉ... cố làm quen thôi! Hơn nữa, giờ tao thấy gắn bó với cái tên này lắm rồi!</t>
         </is>
       </c>
     </row>
@@ -17734,7 +17734,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Tên ta là Abby. Đừng có gọi ta là "nhóc" nữa!</t>
+          <t>Tên tao là Abby. Đừng có gọi tao là "nhóc" nữa!</t>
         </is>
       </c>
     </row>
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Chà, không thành công rồi. Ta cứ tưởng có thể moi được chút thông tin từ cô nhóc... ý ta là Abby, nhưng giờ lại quay về vạch xuất phát.</t>
+          <t>Chà, không thành công rồi. Tao cứ tưởng có thể moi được chút thông tin từ cô nhóc... ý tao là Abby, nhưng giờ lại quay về vạch xuất phát.</t>
         </is>
       </c>
     </row>
@@ -18644,7 +18644,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Hồi đó, tôi chỉ đứng trước mặt {Male=anh ấy;Female=chị ấy}, và con quái vật Threnodian khủng khiếp kia... chỉ đơn giản là... bỏ đi.</t>
+          <t>Hồi đó, tôi chỉ đứng trước mặt {Male=him;Female=her}, và con quái vật Threnodian khủng khiếp kia... chỉ đơn giản là... bỏ đi.</t>
         </is>
       </c>
     </row>
@@ -19164,7 +19164,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Nhưng mà nghĩ xem! Ta đứng yên không làm gì mà còn đánh bại được một con THRENODIAN! Nếu ta mà thực sự ra tay thì không biết sẽ thế nào đấy!</t>
+          <t>Nhưng mà nghĩ xem! Tao đứng yên không làm gì mà còn đánh bại được một con THRENODIAN! Nếu tao mà thực sự ra tay thì không biết sẽ thế nào đấy!</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Tất nhiên! Tớ nói là tớ siêu khỏe mà. Tớ sẽ bảo vệ {Male=cậu ấy;Female=cô ấy}!</t>
+          <t>Tất nhiên! Tớ nói là tớ siêu khỏe mà. Tớ sẽ bảo vệ {Male=him;Female=her}!</t>
         </is>
       </c>
     </row>
@@ -26314,7 +26314,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Haha, vậy là cậu bắt đầu chấp nhận vùng đất mộng mơ này rồi. Vậy thì tiến lên đi.</t>
+          <t>Haha, vậy là mày bắt đầu chấp nhận vùng đất mộng mơ này rồi. Vậy thì tiến lên đi.</t>
         </is>
       </c>
     </row>
@@ -27029,7 +27029,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>...Không sao đâu. Cánh cửa kia còn nhiều điều về giấc mơ mà. Ta tin một ngày nào đó ngươi sẽ tìm ra câu trả lời.</t>
+          <t>...Không sao đâu. Cánh cửa kia còn nhiều điều về giấc mơ mà. Tao tin một ngày nào đó mày sẽ tìm ra câu trả lời.</t>
         </is>
       </c>
     </row>
@@ -27809,7 +27809,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Meow?</t>
+          <t>Meo?</t>
         </is>
       </c>
     </row>
@@ -30409,7 +30409,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Ta chưa thể đưa ra kết luận được. Trước hết, hãy tìm lại mảnh kỳ lạ mà chúng ta từng gặp—cái mà cậu gọi là Dreamless ấy.</t>
+          <t>Tao chưa thể đưa ra kết luận được. Trước hết, hãy tìm lại mảnh kỳ lạ mà chúng ta từng gặp—cái mà cậu gọi là Dreamless ấy.</t>
         </is>
       </c>
     </row>
